--- a/base_datas/mediana_nacional_detalhamento.xlsx
+++ b/base_datas/mediana_nacional_detalhamento.xlsx
@@ -593,46 +593,46 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>515.8657973517559</v>
+        <v>516.0324438722778</v>
       </c>
       <c r="B2">
-        <v>101.8467642907551</v>
+        <v>101.8531463730198</v>
       </c>
       <c r="C2">
-        <v>5932.701288629223</v>
+        <v>5933.843797944526</v>
       </c>
       <c r="D2">
-        <v>223.2961247248556</v>
+        <v>223.5530768653532</v>
       </c>
       <c r="E2">
-        <v>469.3023026519573</v>
+        <v>469.7271447857005</v>
       </c>
       <c r="F2">
-        <v>31.16928503181476</v>
+        <v>31.18702281828407</v>
       </c>
       <c r="G2">
-        <v>1.996446805137149</v>
+        <v>1.991540582496666</v>
       </c>
       <c r="H2">
-        <v>196.7148351898159</v>
+        <v>197.0188182924973</v>
       </c>
       <c r="I2">
-        <v>58.00924209653946</v>
+        <v>58.01528472024993</v>
       </c>
       <c r="J2">
-        <v>6.748062896492199E-15</v>
+        <v>6.678302327223237E-15</v>
       </c>
       <c r="K2">
-        <v>3487.562755576792</v>
+        <v>3489.34398275792</v>
       </c>
       <c r="L2">
-        <v>1421.084529981568</v>
+        <v>1422.77661537327</v>
       </c>
       <c r="M2">
-        <v>928.6885076650015</v>
+        <v>928.9079845745375</v>
       </c>
       <c r="N2">
-        <v>130.3228428588004</v>
+        <v>130.4695659176317</v>
       </c>
       <c r="O2">
         <v>16.78485234836411</v>
@@ -644,19 +644,19 @@
         <v>4.363657591874373</v>
       </c>
       <c r="R2">
-        <v>31.92515055568932</v>
+        <v>31.96501733435998</v>
       </c>
       <c r="S2">
-        <v>44.66321517348305</v>
+        <v>44.77941427002563</v>
       </c>
       <c r="T2">
-        <v>42.31239449133718</v>
+        <v>42.31721031341789</v>
       </c>
       <c r="U2">
-        <v>155.5056274159976</v>
+        <v>155.5723261135215</v>
       </c>
       <c r="V2">
-        <v>165.7407112253642</v>
+        <v>165.8146183256427</v>
       </c>
       <c r="W2">
         <v>3928.699041553994</v>
@@ -665,16 +665,16 @@
         <v>619.6702869300105</v>
       </c>
       <c r="Y2">
-        <v>1.45052265304719E-14</v>
+        <v>1.455412617460216E-14</v>
       </c>
       <c r="Z2">
-        <v>13.67886755341868</v>
+        <v>13.68763877148493</v>
       </c>
       <c r="AA2">
-        <v>17.10469692445506</v>
+        <v>17.1071812969979</v>
       </c>
       <c r="AB2">
-        <v>9.796631039071575E-17</v>
+        <v>9.870513533836118E-17</v>
       </c>
       <c r="AC2">
         <v>1.070917594766341</v>
@@ -686,49 +686,49 @@
         <v>27.84653409123507</v>
       </c>
       <c r="AF2">
-        <v>0.2269675139323094</v>
+        <v>0.2268296770250974</v>
       </c>
       <c r="AG2">
-        <v>2102.126279337749</v>
+        <v>2103.226946250105</v>
       </c>
       <c r="AH2">
         <v>429.4473048975834</v>
       </c>
       <c r="AI2">
-        <v>50.2891568522161</v>
+        <v>50.29455005343783</v>
       </c>
       <c r="AJ2">
-        <v>541.7689916282509</v>
+        <v>541.8739605240122</v>
       </c>
       <c r="AK2">
-        <v>108.9949112991266</v>
+        <v>109.0749637629672</v>
       </c>
       <c r="AL2">
-        <v>200.9990392462349</v>
+        <v>201.171211197722</v>
       </c>
       <c r="AM2">
-        <v>30.04527015192726</v>
+        <v>30.05908632736436</v>
       </c>
       <c r="AN2">
-        <v>58.30464633354965</v>
+        <v>58.37339008199913</v>
       </c>
       <c r="AO2">
-        <v>995.6305699256453</v>
+        <v>996.6229567209978</v>
       </c>
       <c r="AP2">
-        <v>136.4609239640036</v>
+        <v>136.6194532448444</v>
       </c>
       <c r="AQ2">
-        <v>68.10790745151412</v>
+        <v>68.1263232614309</v>
       </c>
       <c r="AR2">
-        <v>8.496211426361437</v>
+        <v>8.505706666979711</v>
       </c>
       <c r="AS2">
-        <v>3.796131058226325</v>
+        <v>3.790412251264306</v>
       </c>
       <c r="AT2">
-        <v>91.28227976170783</v>
+        <v>91.57824656343213</v>
       </c>
       <c r="AU2">
         <v>1</v>
